--- a/연구코드/results/feature_selection/sinchon/feature_selection_summary.xlsx
+++ b/연구코드/results/feature_selection/sinchon/feature_selection_summary.xlsx
@@ -47,7 +47,7 @@
     <t>VIF pruning (VIF&gt;10)</t>
   </si>
   <si>
-    <t>slope_abs_mean, band4_energy, p25, fft_mag_std, valley_count, median, wavelet_cD1_std, range, p75, band1_energy, p10, wavelet_cA_energy, fft_mag_mean, band1_energy_ratio, band4_energy_ratio, p95, wavelet_cA_std, p90, peak_mean_height, AUC_normalized, mean_abs_deviation, peak_max_height, spectral_rolloff, p5, wavelet_energy_ratio_D1, wavelet_cD2_energy, wavelet_cD1_energy, RMSE</t>
+    <t>fft_mag_std, wavelet_cA_std, p90, wavelet_cD1_std, range, p5, p95, band1_energy, RMSE, p75, fft_mag_mean, band4_energy, wavelet_cD2_energy, peak_mean_height, slope_abs_mean, peak_max_height, band1_energy_ratio, wavelet_cD1_energy, wavelet_energy_ratio_D1, p25, p10, AUC_normalized, median, valley_count, wavelet_cA_energy, band4_energy_ratio, mean_abs_deviation, spectral_rolloff</t>
   </si>
   <si>
     <t>AUC, IQR, fft_mag_max, max, peak_count, peak_max_width, peak_mean_width, signal_energy, skewness, slope_mean, slope_min, spectral_centroid, spectral_energy, spectral_spread, wavelet_cD2_std, wavelet_cD3_energy, zero_crossing_rate</t>
@@ -83,12 +83,12 @@
     <t>vote_ge3</t>
   </si>
   <si>
+    <t>vote_ge1</t>
+  </si>
+  <si>
     <t>union_all</t>
   </si>
   <si>
-    <t>vote_ge1</t>
-  </si>
-  <si>
     <t>RF_Perm_only</t>
   </si>
   <si>
@@ -137,97 +137,97 @@
     <t>zero_crossing_rate</t>
   </si>
   <si>
+    <t>p90_p10_ratio</t>
+  </si>
+  <si>
+    <t>peak_mean_width</t>
+  </si>
+  <si>
+    <t>spectral_centroid</t>
+  </si>
+  <si>
     <t>band2_energy_ratio</t>
   </si>
   <si>
-    <t>peak_mean_width</t>
+    <t>fft_mag_max</t>
+  </si>
+  <si>
+    <t>AUC</t>
+  </si>
+  <si>
+    <t>CV</t>
   </si>
   <si>
     <t>slope_mean</t>
   </si>
   <si>
-    <t>p90_p10_ratio</t>
-  </si>
-  <si>
-    <t>fft_mag_max</t>
-  </si>
-  <si>
-    <t>spectral_centroid</t>
-  </si>
-  <si>
-    <t>AUC</t>
-  </si>
-  <si>
-    <t>CV</t>
+    <t>peak_max_width</t>
+  </si>
+  <si>
+    <t>peak_count</t>
   </si>
   <si>
     <t>IQR</t>
   </si>
   <si>
+    <t>skewness</t>
+  </si>
+  <si>
+    <t>kurtosis</t>
+  </si>
+  <si>
+    <t>spectral_spread</t>
+  </si>
+  <si>
+    <t>first_high_pos</t>
+  </si>
+  <si>
+    <t>slope_min</t>
+  </si>
+  <si>
+    <t>slope_std</t>
+  </si>
+  <si>
+    <t>spectral_energy</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>band2_energy</t>
+  </si>
+  <si>
+    <t>wavelet_cD3_std</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>signal_length</t>
+  </si>
+  <si>
+    <t>peak_main_pos</t>
+  </si>
+  <si>
+    <t>signal_energy</t>
+  </si>
+  <si>
+    <t>wavelet_cD2_std</t>
+  </si>
+  <si>
+    <t>wavelet_cD3_energy</t>
+  </si>
+  <si>
+    <t>band3_energy_ratio</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>dominant_freq</t>
+  </si>
+  <si>
     <t>slope_max</t>
-  </si>
-  <si>
-    <t>first_high_pos</t>
-  </si>
-  <si>
-    <t>signal_energy</t>
-  </si>
-  <si>
-    <t>band2_energy</t>
-  </si>
-  <si>
-    <t>peak_max_width</t>
-  </si>
-  <si>
-    <t>wavelet_cD2_std</t>
-  </si>
-  <si>
-    <t>std</t>
-  </si>
-  <si>
-    <t>dominant_freq</t>
-  </si>
-  <si>
-    <t>spectral_spread</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>band3_energy_ratio</t>
-  </si>
-  <si>
-    <t>skewness</t>
-  </si>
-  <si>
-    <t>slope_min</t>
-  </si>
-  <si>
-    <t>signal_length</t>
-  </si>
-  <si>
-    <t>wavelet_cD3_std</t>
-  </si>
-  <si>
-    <t>peak_count</t>
-  </si>
-  <si>
-    <t>slope_std</t>
-  </si>
-  <si>
-    <t>spectral_energy</t>
-  </si>
-  <si>
-    <t>wavelet_cD3_energy</t>
-  </si>
-  <si>
-    <t>kurtosis</t>
-  </si>
-  <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>peak_main_pos</t>
   </si>
   <si>
     <t>peak_std_height</t>
@@ -701,7 +701,7 @@
         <v>17</v>
       </c>
       <c r="C2">
-        <v>0.098763750553166</v>
+        <v>0.09876375055316595</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -715,7 +715,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>0.09422121001868564</v>
+        <v>0.09422121001868559</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -729,7 +729,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>0.07513415392997251</v>
+        <v>0.07513415392997255</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -743,7 +743,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>0.05922520891076251</v>
+        <v>0.05922520891076237</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
@@ -757,7 +757,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0.05771111288514297</v>
+        <v>0.05771111288514301</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -771,7 +771,7 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>-0.147781495176765</v>
+        <v>-0.1477814951767675</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
@@ -785,7 +785,7 @@
         <v>33</v>
       </c>
       <c r="C8">
-        <v>-0.1477814951767661</v>
+        <v>-0.1477814951767684</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
@@ -799,7 +799,7 @@
         <v>33</v>
       </c>
       <c r="C9">
-        <v>-0.1477814951767677</v>
+        <v>-0.1477814951767686</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
@@ -910,13 +910,13 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>0.05680607666697224</v>
+        <v>0.02467660868363675</v>
       </c>
       <c r="G4">
-        <v>0.009097645213949538</v>
+        <v>-0.1223260580122692</v>
       </c>
       <c r="H4">
-        <v>0.7459164427607015</v>
+        <v>1.224391247864785E-05</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -953,22 +953,22 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.001738440350150139</v>
       </c>
       <c r="G6">
-        <v>0.06899528972260857</v>
+        <v>0.06119722045541939</v>
       </c>
       <c r="H6">
-        <v>0.01388328883776795</v>
+        <v>0.02913568790884516</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -988,13 +988,13 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.02467660868363675</v>
+        <v>0.05680607666697224</v>
       </c>
       <c r="G7">
-        <v>-0.1223260580122692</v>
+        <v>0.009097645213949538</v>
       </c>
       <c r="H7">
-        <v>1.224391247864785E-05</v>
+        <v>0.7459164427607015</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1031,22 +1031,22 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>0.001738440350150139</v>
+        <v>0.02685575363017101</v>
       </c>
       <c r="G9">
-        <v>0.06119722045541939</v>
+        <v>0.2158179640102999</v>
       </c>
       <c r="H9">
-        <v>0.02913568790884516</v>
+        <v>7.343747734458469E-15</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.02685575363017101</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>0.2158179640102999</v>
+        <v>-0.131354028217828</v>
       </c>
       <c r="H10">
-        <v>7.343747734458469E-15</v>
+        <v>2.618507265846386E-06</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>-0.131354028217828</v>
+        <v>0.06899528972260857</v>
       </c>
       <c r="H11">
-        <v>2.618507265846386E-06</v>
+        <v>0.01388328883776795</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1118,13 +1118,13 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>0.0001064739115430591</v>
+        <v>0.01931159189417242</v>
       </c>
       <c r="G12">
-        <v>-0.02209183542907095</v>
+        <v>0.1003944159289539</v>
       </c>
       <c r="H12">
-        <v>0.431329258732049</v>
+        <v>0.0003374551254947321</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1144,13 +1144,13 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>0.003065626782587927</v>
+        <v>0.01697616447823336</v>
       </c>
       <c r="G13">
-        <v>0.2124966331294762</v>
+        <v>0.08922313682577719</v>
       </c>
       <c r="H13">
-        <v>1.919939657764731E-14</v>
+        <v>0.001451926713498682</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1170,13 +1170,13 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>0.02183813124742073</v>
+        <v>0.0001064739115430591</v>
       </c>
       <c r="G14">
-        <v>0.02520720991881296</v>
+        <v>-0.02209183542907095</v>
       </c>
       <c r="H14">
-        <v>0.3692266617451234</v>
+        <v>0.431329258732049</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.00416031262364136</v>
       </c>
       <c r="G15">
-        <v>0.2216348340319491</v>
+        <v>-0.06016177884717459</v>
       </c>
       <c r="H15">
-        <v>1.313079481857501E-15</v>
+        <v>0.03197962040409952</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1222,13 +1222,13 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>0.005520957338708055</v>
+        <v>0.02317873999776143</v>
       </c>
       <c r="G16">
-        <v>0.03846285222041766</v>
+        <v>0.1840964913884834</v>
       </c>
       <c r="H16">
-        <v>0.1705619525091443</v>
+        <v>3.756308236071874E-11</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1248,13 +1248,13 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>0.01931159189417242</v>
+        <v>0.0100516165813227</v>
       </c>
       <c r="G17">
-        <v>0.1003944159289539</v>
+        <v>0.000204487370416031</v>
       </c>
       <c r="H17">
-        <v>0.0003374551254947321</v>
+        <v>0.9941890388816222</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1274,13 +1274,13 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>0.05248366657931935</v>
+        <v>0.02183813124742073</v>
       </c>
       <c r="G18">
-        <v>0.1733840996662887</v>
+        <v>0.02520720991881296</v>
       </c>
       <c r="H18">
-        <v>4.894997707133988E-10</v>
+        <v>0.3692266617451234</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1300,13 +1300,13 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>0.03796568588434379</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>0.03275000019090109</v>
+        <v>-0.1840675505765382</v>
       </c>
       <c r="H19">
-        <v>0.2433164866149352</v>
+        <v>3.783255740618084E-11</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>0.07376464842085761</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>-0.05862626251613298</v>
+        <v>0.2045972503771621</v>
       </c>
       <c r="H20">
-        <v>0.03663297245911071</v>
+        <v>1.771735228659869E-13</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1352,13 +1352,13 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>0.0100516165813227</v>
+        <v>0.02665402921515936</v>
       </c>
       <c r="G21">
-        <v>0.000204487370416031</v>
+        <v>0.05227088441037193</v>
       </c>
       <c r="H21">
-        <v>0.9941890388816222</v>
+        <v>0.06246875221612761</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1378,13 +1378,13 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>0.03670529154184354</v>
       </c>
       <c r="G22">
-        <v>0.2311231494201107</v>
+        <v>0.2238189057127703</v>
       </c>
       <c r="H22">
-        <v>7.126123145518417E-17</v>
+        <v>6.793151437168481E-16</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1404,13 +1404,13 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>0.009241468356806948</v>
+        <v>0.005520957338708055</v>
       </c>
       <c r="G23">
-        <v>-0.001140861960857506</v>
+        <v>0.03846285222041766</v>
       </c>
       <c r="H23">
-        <v>0.9675885050856522</v>
+        <v>0.1705619525091443</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1430,13 +1430,13 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>0.00416031262364136</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>-0.06016177884717459</v>
+        <v>0.116408059406549</v>
       </c>
       <c r="H24">
-        <v>0.03197962040409952</v>
+        <v>3.180513501099747E-05</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>0.03796568588434379</v>
       </c>
       <c r="G25">
-        <v>-0.1840675505765382</v>
+        <v>0.03275000019090109</v>
       </c>
       <c r="H25">
-        <v>3.783255740618084E-11</v>
+        <v>0.2433164866149352</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1511,10 +1511,10 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0.116408059406549</v>
+        <v>0.07162353270483773</v>
       </c>
       <c r="H27">
-        <v>3.180513501099747E-05</v>
+        <v>0.01064243788129301</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1534,13 +1534,13 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>0.01697616447823336</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>0.08922313682577719</v>
+        <v>0.2216348340319491</v>
       </c>
       <c r="H28">
-        <v>0.001451926713498682</v>
+        <v>1.313079481857501E-15</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1560,13 +1560,13 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>0.05248366657931935</v>
       </c>
       <c r="G29">
-        <v>0.2045972503771621</v>
+        <v>0.1733840996662887</v>
       </c>
       <c r="H29">
-        <v>1.771735228659869E-13</v>
+        <v>4.894997707133988E-10</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>0.02665402921515936</v>
+        <v>0.01244173464559628</v>
       </c>
       <c r="G30">
-        <v>0.05227088441037193</v>
+        <v>0.133370110268565</v>
       </c>
       <c r="H30">
-        <v>0.06246875221612761</v>
+        <v>1.829119265022864E-06</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1612,13 +1612,13 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>0.01244173464559628</v>
+        <v>0.009241468356806948</v>
       </c>
       <c r="G31">
-        <v>0.133370110268565</v>
+        <v>-0.001140861960857506</v>
       </c>
       <c r="H31">
-        <v>1.829119265022864E-06</v>
+        <v>0.9675885050856522</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1638,13 +1638,13 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>0.02317873999776143</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>0.1840964913884834</v>
+        <v>0.2311231494201107</v>
       </c>
       <c r="H32">
-        <v>3.756308236071874E-11</v>
+        <v>7.126123145518417E-17</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1664,13 +1664,13 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>0.03670529154184354</v>
+        <v>0.07376464842085761</v>
       </c>
       <c r="G33">
-        <v>0.2238189057127703</v>
+        <v>-0.05862626251613298</v>
       </c>
       <c r="H33">
-        <v>6.793151437168481E-16</v>
+        <v>0.03663297245911071</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1690,13 +1690,13 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>0.003065626782587927</v>
       </c>
       <c r="G34">
-        <v>0.07162353270483773</v>
+        <v>0.2124966331294762</v>
       </c>
       <c r="H34">
-        <v>0.01064243788129301</v>
+        <v>1.919939657764731E-14</v>
       </c>
     </row>
   </sheetData>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B3">
         <v>0.07376464842085761</v>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <v>0.05680607666697224</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>0.05248366657931935</v>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B7">
         <v>0.03796568588434379</v>
@@ -1809,7 +1809,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B8">
         <v>0.03670529154184354</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9">
         <v>0.02685575363017101</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B10">
         <v>0.02665402921515936</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>0.02467660868363675</v>
@@ -1865,7 +1865,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B12">
         <v>0.02317873999776143</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B13">
         <v>0.02183813124742073</v>
@@ -1893,7 +1893,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>0.01931159189417242</v>
@@ -1935,7 +1935,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B17">
         <v>0.01697616447823336</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18">
         <v>0.01244173464559628</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B20">
         <v>0.0100516165813227</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B21">
         <v>0.009241468356806948</v>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B22">
         <v>0.005520957338708055</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B23">
         <v>0.00416031262364136</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B24">
         <v>0.003065626782587927</v>
@@ -2047,7 +2047,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B25">
         <v>0.001738440350150139</v>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B26">
         <v>0.0001064739115430591</v>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2145,7 +2145,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2173,7 +2173,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B3">
         <v>766.229327687265</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B4">
         <v>363.4626769355639</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B5">
         <v>316.4109499953126</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>159.0133372106835</v>
@@ -2301,7 +2301,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>148.7113016225247</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B8">
         <v>147.5171717141093</v>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>121.4257923588872</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>96.13214918834973</v>
@@ -2349,7 +2349,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B13">
         <v>73.9592654958339</v>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B15">
         <v>58.59776609909621</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B16">
         <v>58.31107383422511</v>
@@ -2381,7 +2381,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>52.91039906801216</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B18">
         <v>33.03756809422134</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B19">
         <v>31.39750788081958</v>
@@ -2413,7 +2413,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B21">
         <v>24.53475098731074</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <v>20.6836399016506</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B23">
         <v>17.15586565945858</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B24">
         <v>16.0591588837813</v>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B25">
         <v>14.73224750748778</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B26">
         <v>13.43059426558227</v>
@@ -2461,7 +2461,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B27">
         <v>12.48695053312343</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B28">
         <v>11.74781658715669</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B29">
         <v>11.25341924613849</v>
@@ -2493,7 +2493,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B31">
         <v>8.249551284409103</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B32">
         <v>8.184992379074702</v>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B36">
         <v>4.122012534788953</v>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B37">
         <v>3.605153515701735</v>
@@ -2549,7 +2549,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B38">
         <v>3.555278190690234</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B3">
         <v>326.0494693294132</v>
@@ -2611,7 +2611,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>41.87324484419293</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>25.75729442576642</v>
@@ -2633,7 +2633,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <v>25.66458474694967</v>
@@ -2644,7 +2644,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8">
         <v>20.42611737638902</v>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B9">
         <v>18.46828252636565</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B10">
         <v>12.1962710506586</v>
@@ -2677,7 +2677,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B11">
         <v>9.778753757203608</v>
@@ -2699,7 +2699,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B13">
         <v>7.923688843187629</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>7.534019274019623</v>
@@ -2721,7 +2721,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B15">
         <v>6.250986981492523</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B17">
         <v>4.426767255194977</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>2.02520703580745</v>
@@ -2765,7 +2765,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19">
         <v>1.979926948591125</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20">
         <v>41.87290280834648</v>
@@ -2798,7 +2798,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>36.28813888109696</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B23">
         <v>25.10452393526627</v>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B24">
         <v>24.88224502734892</v>
@@ -2831,7 +2831,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B25">
         <v>20.38911572387227</v>
@@ -2842,7 +2842,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B26">
         <v>16.76324080280147</v>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B27">
         <v>12.18919840526254</v>
@@ -2864,7 +2864,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B28">
         <v>8.941543249683734</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B30">
         <v>7.80286786728263</v>
@@ -2897,7 +2897,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B31">
         <v>6.445186308519587</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B33">
         <v>5.80782290908279</v>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B34">
         <v>4.351265437384765</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B35">
         <v>1.956215191063303</v>
@@ -2952,7 +2952,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B36">
         <v>1.433111657979802</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B37">
         <v>31.92581828342628</v>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B39">
         <v>24.7124415882073</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B40">
         <v>24.41952041322764</v>
@@ -3007,7 +3007,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B41">
         <v>17.37516368766268</v>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B42">
         <v>12.57042430662915</v>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B43">
         <v>9.930809114650833</v>
@@ -3040,7 +3040,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B44">
         <v>8.916704995121531</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B46">
         <v>7.76003933921245</v>
@@ -3073,7 +3073,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B47">
         <v>6.063529971232985</v>
@@ -3095,7 +3095,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B49">
         <v>5.606672849834768</v>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B50">
         <v>4.192989756761937</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B51">
         <v>1.95370051405314</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B52">
         <v>1.432796266342846</v>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B53">
         <v>31.84122748155631</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B54">
         <v>24.21651697444816</v>
@@ -3161,7 +3161,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B55">
         <v>24.19050525811368</v>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B56">
         <v>12.46761279135353</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B57">
         <v>9.445798538099208</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B58">
         <v>8.789333686335024</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B60">
         <v>7.697158278886958</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B61">
         <v>6.564858461468513</v>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B63">
         <v>5.392694578619995</v>
@@ -3260,7 +3260,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B64">
         <v>4.186151772503821</v>
@@ -3271,7 +3271,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B65">
         <v>2.471635140572852</v>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66">
         <v>1.953644650973072</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B67">
         <v>1.40530325996088</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B68">
         <v>22.54677861593612</v>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B69">
         <v>10.15960246376948</v>
@@ -3326,7 +3326,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B70">
         <v>9.052538571684716</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B71">
         <v>8.737655559807953</v>
@@ -3359,7 +3359,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B73">
         <v>7.697114662154104</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B74">
         <v>7.582889283365247</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B75">
         <v>6.431520964206865</v>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B77">
         <v>5.374637695971954</v>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B78">
         <v>3.234197776257935</v>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B79">
         <v>2.334493933447929</v>
@@ -3436,7 +3436,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B80">
         <v>1.949651365211263</v>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B81">
         <v>1.400793796367297</v>
@@ -3458,7 +3458,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B82">
         <v>9.036720426049223</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B83">
         <v>8.619731447308707</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B85">
         <v>7.597470939743933</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B86">
         <v>7.591424209270143</v>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B87">
         <v>7.137077464490902</v>
@@ -3535,7 +3535,7 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B89">
         <v>5.369596816373703</v>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B90">
         <v>5.297119430349436</v>
@@ -3557,7 +3557,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B91">
         <v>3.206427328735217</v>
@@ -3568,7 +3568,7 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B92">
         <v>1.946139302455396</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B93">
         <v>1.604938015926638</v>
@@ -3590,7 +3590,7 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B94">
         <v>1.373557923280666</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B2">
         <v>9.036720426049223</v>
@@ -3627,7 +3627,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B3">
         <v>8.619731447308707</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>7.597470939743933</v>
@@ -3651,7 +3651,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>7.591424209270143</v>
@@ -3659,7 +3659,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B7">
         <v>7.137077464490902</v>
@@ -3675,7 +3675,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B9">
         <v>5.369596816373703</v>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10">
         <v>5.297119430349436</v>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <v>3.206427328735217</v>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12">
         <v>1.946139302455396</v>
@@ -3707,7 +3707,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B13">
         <v>1.604938015926638</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B14">
         <v>1.373557923280666</v>
@@ -3738,22 +3738,22 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -3763,37 +3763,37 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:1">

--- a/연구코드/results/feature_selection/sinchon/feature_selection_summary.xlsx
+++ b/연구코드/results/feature_selection/sinchon/feature_selection_summary.xlsx
@@ -47,7 +47,7 @@
     <t>VIF pruning (VIF&gt;10)</t>
   </si>
   <si>
-    <t>fft_mag_std, wavelet_cA_std, p90, wavelet_cD1_std, range, p5, p95, band1_energy, RMSE, p75, fft_mag_mean, band4_energy, wavelet_cD2_energy, peak_mean_height, slope_abs_mean, peak_max_height, band1_energy_ratio, wavelet_cD1_energy, wavelet_energy_ratio_D1, p25, p10, AUC_normalized, median, valley_count, wavelet_cA_energy, band4_energy_ratio, mean_abs_deviation, spectral_rolloff</t>
+    <t>wavelet_cD2_energy, range, peak_mean_height, p5, wavelet_energy_ratio_D1, fft_mag_std, AUC_normalized, wavelet_cA_energy, spectral_rolloff, mean_abs_deviation, p95, p75, RMSE, valley_count, band1_energy_ratio, band1_energy, band4_energy_ratio, wavelet_cD1_energy, p90, wavelet_cA_std, median, slope_abs_mean, wavelet_cD1_std, band4_energy, fft_mag_mean, peak_max_height, p10, p25</t>
   </si>
   <si>
     <t>AUC, IQR, fft_mag_max, max, peak_count, peak_max_width, peak_mean_width, signal_energy, skewness, slope_mean, slope_min, spectral_centroid, spectral_energy, spectral_spread, wavelet_cD2_std, wavelet_cD3_energy, zero_crossing_rate</t>
@@ -131,34 +131,40 @@
     <t>p_value</t>
   </si>
   <si>
+    <t>zero_crossing_rate</t>
+  </si>
+  <si>
     <t>max</t>
   </si>
   <si>
-    <t>zero_crossing_rate</t>
+    <t>fft_mag_max</t>
+  </si>
+  <si>
+    <t>spectral_centroid</t>
+  </si>
+  <si>
+    <t>slope_mean</t>
+  </si>
+  <si>
+    <t>AUC</t>
   </si>
   <si>
     <t>p90_p10_ratio</t>
   </si>
   <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>peak_mean_width</t>
   </si>
   <si>
-    <t>spectral_centroid</t>
-  </si>
-  <si>
     <t>band2_energy_ratio</t>
   </si>
   <si>
-    <t>fft_mag_max</t>
-  </si>
-  <si>
-    <t>AUC</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>slope_mean</t>
+    <t>dominant_freq</t>
+  </si>
+  <si>
+    <t>band3_energy_ratio</t>
   </si>
   <si>
     <t>peak_max_width</t>
@@ -170,70 +176,64 @@
     <t>IQR</t>
   </si>
   <si>
+    <t>spectral_spread</t>
+  </si>
+  <si>
+    <t>wavelet_cD3_energy</t>
+  </si>
+  <si>
+    <t>slope_std</t>
+  </si>
+  <si>
+    <t>signal_energy</t>
+  </si>
+  <si>
+    <t>kurtosis</t>
+  </si>
+  <si>
+    <t>first_high_pos</t>
+  </si>
+  <si>
+    <t>wavelet_cD3_std</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>band2_energy</t>
+  </si>
+  <si>
+    <t>slope_max</t>
+  </si>
+  <si>
+    <t>peak_main_pos</t>
+  </si>
+  <si>
+    <t>slope_min</t>
+  </si>
+  <si>
     <t>skewness</t>
   </si>
   <si>
-    <t>kurtosis</t>
-  </si>
-  <si>
-    <t>spectral_spread</t>
-  </si>
-  <si>
-    <t>first_high_pos</t>
-  </si>
-  <si>
-    <t>slope_min</t>
-  </si>
-  <si>
-    <t>slope_std</t>
+    <t>wavelet_cD2_std</t>
   </si>
   <si>
     <t>spectral_energy</t>
   </si>
   <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>band2_energy</t>
-  </si>
-  <si>
-    <t>wavelet_cD3_std</t>
+    <t>min</t>
+  </si>
+  <si>
+    <t>signal_length</t>
   </si>
   <si>
     <t>std</t>
   </si>
   <si>
-    <t>signal_length</t>
-  </si>
-  <si>
-    <t>peak_main_pos</t>
-  </si>
-  <si>
-    <t>signal_energy</t>
-  </si>
-  <si>
-    <t>wavelet_cD2_std</t>
-  </si>
-  <si>
-    <t>wavelet_cD3_energy</t>
-  </si>
-  <si>
-    <t>band3_energy_ratio</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>dominant_freq</t>
-  </si>
-  <si>
-    <t>slope_max</t>
+    <t>peak_last_pos</t>
   </si>
   <si>
     <t>peak_std_height</t>
-  </si>
-  <si>
-    <t>peak_last_pos</t>
   </si>
   <si>
     <t>peak_first_pos</t>
@@ -701,7 +701,7 @@
         <v>17</v>
       </c>
       <c r="C2">
-        <v>0.09876375055316595</v>
+        <v>0.098763750553166</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -715,7 +715,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>0.09422121001868559</v>
+        <v>0.09422121001868569</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -729,7 +729,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>0.07513415392997255</v>
+        <v>0.07513415392997244</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -743,7 +743,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>0.05922520891076237</v>
+        <v>0.05922520891076235</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
@@ -771,7 +771,7 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>-0.1477814951767675</v>
+        <v>-0.1477814951767644</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
@@ -785,7 +785,7 @@
         <v>33</v>
       </c>
       <c r="C8">
-        <v>-0.1477814951767684</v>
+        <v>-0.1477814951767654</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
@@ -799,7 +799,7 @@
         <v>33</v>
       </c>
       <c r="C9">
-        <v>-0.1477814951767686</v>
+        <v>-0.1477814951767658</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
@@ -858,13 +858,13 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.01060986752624382</v>
+        <v>0.0654025856735676</v>
       </c>
       <c r="G2">
-        <v>0.1997601737185831</v>
+        <v>0.1785938877945625</v>
       </c>
       <c r="H2">
-        <v>6.612496588809641E-13</v>
+        <v>1.432264850401951E-10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -884,13 +884,13 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.0654025856735676</v>
+        <v>0.01060986752624382</v>
       </c>
       <c r="G3">
-        <v>0.1785938877945625</v>
+        <v>0.1997601737185831</v>
       </c>
       <c r="H3">
-        <v>1.432264850401951E-10</v>
+        <v>6.612496588809641E-13</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -901,22 +901,22 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>0.02467660868363675</v>
+        <v>0.0170287002512044</v>
       </c>
       <c r="G4">
-        <v>-0.1223260580122692</v>
+        <v>0.01414262849277602</v>
       </c>
       <c r="H4">
-        <v>1.224391247864785E-05</v>
+        <v>0.6144517034028094</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -927,22 +927,22 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.01760399500620879</v>
+        <v>0.001738440350150139</v>
       </c>
       <c r="G5">
-        <v>0.01376479737486372</v>
+        <v>0.06119722045541939</v>
       </c>
       <c r="H5">
-        <v>0.6239425888046031</v>
+        <v>0.02913568790884516</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -953,22 +953,22 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0.001738440350150139</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>0.06119722045541939</v>
+        <v>0.06899528972260857</v>
       </c>
       <c r="H6">
-        <v>0.02913568790884516</v>
+        <v>0.01388328883776795</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -988,13 +988,13 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.05680607666697224</v>
+        <v>0.02685575363017101</v>
       </c>
       <c r="G7">
-        <v>0.009097645213949538</v>
+        <v>0.2158179640102999</v>
       </c>
       <c r="H7">
-        <v>0.7459164427607015</v>
+        <v>7.343747734458469E-15</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1005,22 +1005,22 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.0170287002512044</v>
+        <v>0.02467660868363675</v>
       </c>
       <c r="G8">
-        <v>0.01414262849277602</v>
+        <v>-0.1223260580122692</v>
       </c>
       <c r="H8">
-        <v>0.6144517034028094</v>
+        <v>1.224391247864785E-05</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1040,13 +1040,13 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>0.02685575363017101</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>0.2158179640102999</v>
+        <v>-0.131354028217828</v>
       </c>
       <c r="H9">
-        <v>7.343747734458469E-15</v>
+        <v>2.618507265846387E-06</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.01760399500620879</v>
       </c>
       <c r="G10">
-        <v>-0.131354028217828</v>
+        <v>0.01376479737486372</v>
       </c>
       <c r="H10">
-        <v>2.618507265846386E-06</v>
+        <v>0.6239425888046031</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1092,13 +1092,13 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.05680607666697224</v>
       </c>
       <c r="G11">
-        <v>0.06899528972260857</v>
+        <v>0.009097645213949538</v>
       </c>
       <c r="H11">
-        <v>0.01388328883776795</v>
+        <v>0.7459164427607015</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1118,13 +1118,13 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>0.01931159189417242</v>
+        <v>0.07376464842085761</v>
       </c>
       <c r="G12">
-        <v>0.1003944159289539</v>
+        <v>-0.05862626251613298</v>
       </c>
       <c r="H12">
-        <v>0.0003374551254947321</v>
+        <v>0.03663297245911071</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1144,13 +1144,13 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>0.01697616447823336</v>
+        <v>0.009241468356806948</v>
       </c>
       <c r="G13">
-        <v>0.08922313682577719</v>
+        <v>-0.001140861960857506</v>
       </c>
       <c r="H13">
-        <v>0.001451926713498682</v>
+        <v>0.9675885050856522</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1170,13 +1170,13 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>0.0001064739115430591</v>
+        <v>0.01931159189417242</v>
       </c>
       <c r="G14">
-        <v>-0.02209183542907095</v>
+        <v>0.1003944159289539</v>
       </c>
       <c r="H14">
-        <v>0.431329258732049</v>
+        <v>0.0003374551254947321</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>0.00416031262364136</v>
+        <v>0.01697616447823336</v>
       </c>
       <c r="G15">
-        <v>-0.06016177884717459</v>
+        <v>0.08922313682577719</v>
       </c>
       <c r="H15">
-        <v>0.03197962040409952</v>
+        <v>0.001451926713498682</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1222,13 +1222,13 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>0.02317873999776143</v>
+        <v>0.0001064739115430591</v>
       </c>
       <c r="G16">
-        <v>0.1840964913884834</v>
+        <v>-0.02209183542907095</v>
       </c>
       <c r="H16">
-        <v>3.756308236071874E-11</v>
+        <v>0.431329258732049</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1274,13 +1274,13 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>0.02183813124742073</v>
+        <v>0.01244173464559628</v>
       </c>
       <c r="G18">
-        <v>0.02520720991881296</v>
+        <v>0.133370110268565</v>
       </c>
       <c r="H18">
-        <v>0.3692266617451234</v>
+        <v>1.829119265022864E-06</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1303,10 +1303,10 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>-0.1840675505765382</v>
+        <v>0.2045972503771621</v>
       </c>
       <c r="H19">
-        <v>3.783255740618084E-11</v>
+        <v>1.771735228659869E-13</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1329,10 +1329,10 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0.2045972503771621</v>
+        <v>0.2216348340319491</v>
       </c>
       <c r="H20">
-        <v>1.771735228659869E-13</v>
+        <v>1.313079481857501E-15</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1352,13 +1352,13 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>0.02665402921515936</v>
+        <v>0.02317873999776143</v>
       </c>
       <c r="G21">
-        <v>0.05227088441037193</v>
+        <v>0.1840964913884834</v>
       </c>
       <c r="H21">
-        <v>0.06246875221612761</v>
+        <v>3.756308236071874E-11</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1378,13 +1378,13 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>0.03670529154184354</v>
+        <v>0.02183813124742073</v>
       </c>
       <c r="G22">
-        <v>0.2238189057127703</v>
+        <v>0.02520720991881296</v>
       </c>
       <c r="H22">
-        <v>6.793151437168481E-16</v>
+        <v>0.3692266617451235</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1404,13 +1404,13 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>0.005520957338708055</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>0.03846285222041766</v>
+        <v>0.116408059406549</v>
       </c>
       <c r="H23">
-        <v>0.1705619525091443</v>
+        <v>3.180513501099746E-05</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1430,13 +1430,13 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>0.03670529154184354</v>
       </c>
       <c r="G24">
-        <v>0.116408059406549</v>
+        <v>0.2238189057127703</v>
       </c>
       <c r="H24">
-        <v>3.180513501099747E-05</v>
+        <v>6.793151437168481E-16</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>0.03796568588434379</v>
+        <v>0.005520957338708055</v>
       </c>
       <c r="G25">
-        <v>0.03275000019090109</v>
+        <v>0.03846285222041766</v>
       </c>
       <c r="H25">
-        <v>0.2433164866149352</v>
+        <v>0.1705619525091443</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1482,13 +1482,13 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>0.08346266882108866</v>
+        <v>0.003065626782587927</v>
       </c>
       <c r="G26">
-        <v>0.1874827253801424</v>
+        <v>0.2124966331294762</v>
       </c>
       <c r="H26">
-        <v>1.614546679236788E-11</v>
+        <v>1.919939657764731E-14</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.2216348340319491</v>
+        <v>-0.1840675505765382</v>
       </c>
       <c r="H28">
-        <v>1.313079481857501E-15</v>
+        <v>3.783255740618084E-11</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1560,13 +1560,13 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>0.05248366657931935</v>
+        <v>0.00416031262364136</v>
       </c>
       <c r="G29">
-        <v>0.1733840996662887</v>
+        <v>-0.06016177884717459</v>
       </c>
       <c r="H29">
-        <v>4.894997707133988E-10</v>
+        <v>0.03197962040409953</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>0.01244173464559628</v>
+        <v>0.05248366657931935</v>
       </c>
       <c r="G30">
-        <v>0.133370110268565</v>
+        <v>0.1733840996662887</v>
       </c>
       <c r="H30">
-        <v>1.829119265022864E-06</v>
+        <v>4.894997707133989E-10</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1612,13 +1612,13 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>0.009241468356806948</v>
+        <v>0.02665402921515936</v>
       </c>
       <c r="G31">
-        <v>-0.001140861960857506</v>
+        <v>0.05227088441037193</v>
       </c>
       <c r="H31">
-        <v>0.9675885050856522</v>
+        <v>0.06246875221612761</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1664,13 +1664,13 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>0.07376464842085761</v>
+        <v>0.08346266882108866</v>
       </c>
       <c r="G33">
-        <v>-0.05862626251613298</v>
+        <v>0.1874827253801424</v>
       </c>
       <c r="H33">
-        <v>0.03663297245911071</v>
+        <v>1.614546679236788E-11</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1690,13 +1690,13 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>0.003065626782587927</v>
+        <v>0.03796568588434379</v>
       </c>
       <c r="G34">
-        <v>0.2124966331294762</v>
+        <v>0.03275000019090109</v>
       </c>
       <c r="H34">
-        <v>1.919939657764731E-14</v>
+        <v>0.2433164866149352</v>
       </c>
     </row>
   </sheetData>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B2">
         <v>0.08346266882108866</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B3">
         <v>0.07376464842085761</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0.0654025856735676</v>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>0.05680607666697224</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6">
         <v>0.05248366657931935</v>
@@ -1790,12 +1790,12 @@
         <v>0.1733840996662887</v>
       </c>
       <c r="D6">
-        <v>4.894997707133988E-10</v>
+        <v>4.894997707133989E-10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B7">
         <v>0.03796568588434379</v>
@@ -1809,7 +1809,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8">
         <v>0.03670529154184354</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>0.02685575363017101</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B10">
         <v>0.02665402921515936</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <v>0.02467660868363675</v>
@@ -1865,7 +1865,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B12">
         <v>0.02317873999776143</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B13">
         <v>0.02183813124742073</v>
@@ -1888,12 +1888,12 @@
         <v>0.02520720991881296</v>
       </c>
       <c r="D13">
-        <v>0.3692266617451234</v>
+        <v>0.3692266617451235</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B14">
         <v>0.01931159189417242</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B15">
         <v>0.01760399500620879</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B16">
         <v>0.0170287002512044</v>
@@ -1935,7 +1935,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B17">
         <v>0.01697616447823336</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <v>0.01244173464559628</v>
@@ -1963,7 +1963,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19">
         <v>0.01060986752624382</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B21">
         <v>0.009241468356806948</v>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B22">
         <v>0.005520957338708055</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B23">
         <v>0.00416031262364136</v>
@@ -2028,12 +2028,12 @@
         <v>-0.06016177884717459</v>
       </c>
       <c r="D23">
-        <v>0.03197962040409952</v>
+        <v>0.03197962040409953</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B24">
         <v>0.003065626782587927</v>
@@ -2047,7 +2047,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25">
         <v>0.001738440350150139</v>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B26">
         <v>0.0001064739115430591</v>
@@ -2075,21 +2075,21 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.2311231494201107</v>
+        <v>0.02782971538947907</v>
       </c>
       <c r="D27">
-        <v>7.126123145518417E-17</v>
+        <v>0.3215023059479291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2098,12 +2098,12 @@
         <v>-0.131354028217828</v>
       </c>
       <c r="D28">
-        <v>2.618507265846386E-06</v>
+        <v>2.618507265846387E-06</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2131,86 +2131,86 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>0.2045972503771621</v>
+        <v>-0.001178186297915739</v>
       </c>
       <c r="D31">
-        <v>1.771735228659869E-13</v>
+        <v>0.9665287451927558</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>0.06899528972260857</v>
+        <v>0.2311231494201107</v>
       </c>
       <c r="D32">
-        <v>0.01388328883776795</v>
+        <v>7.126123145518417E-17</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0.02782971538947907</v>
+        <v>0.07162353270483773</v>
       </c>
       <c r="D33">
-        <v>0.3215023059479291</v>
+        <v>0.01064243788129301</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0.07162353270483773</v>
+        <v>0.2045972503771621</v>
       </c>
       <c r="D34">
-        <v>0.01064243788129301</v>
+        <v>1.771735228659869E-13</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>-0.001178186297915739</v>
+        <v>-0.1840675505765382</v>
       </c>
       <c r="D35">
-        <v>0.9665287451927558</v>
+        <v>3.783255740618084E-11</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>-0.1840675505765382</v>
+        <v>0.116408059406549</v>
       </c>
       <c r="D36">
-        <v>3.783255740618084E-11</v>
+        <v>3.180513501099746E-05</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2229,16 +2229,16 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0.116408059406549</v>
+        <v>0.06899528972260857</v>
       </c>
       <c r="D38">
-        <v>3.180513501099747E-05</v>
+        <v>0.01388328883776795</v>
       </c>
     </row>
   </sheetData>
@@ -2261,7 +2261,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>1289.284989699355</v>
@@ -2269,7 +2269,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3">
         <v>766.229327687265</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B4">
         <v>363.4626769355639</v>
@@ -2293,23 +2293,23 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B6">
-        <v>159.0133372106835</v>
+        <v>159.0133372106722</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7">
-        <v>148.7113016225247</v>
+        <v>148.7113016225222</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8">
         <v>147.5171717141093</v>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <v>121.4257923588872</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>96.13214918834973</v>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B12">
         <v>82.42884405187472</v>
@@ -2352,12 +2352,12 @@
         <v>51</v>
       </c>
       <c r="B13">
-        <v>73.9592654958339</v>
+        <v>73.95926549583329</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B14">
         <v>71.79632406955261</v>
@@ -2365,15 +2365,15 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B15">
-        <v>58.59776609909621</v>
+        <v>58.59776609909582</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B16">
         <v>58.31107383422511</v>
@@ -2381,31 +2381,31 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B17">
-        <v>52.91039906801216</v>
+        <v>52.91039906801186</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B18">
-        <v>33.03756809422134</v>
+        <v>33.03756809422122</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B19">
-        <v>31.39750788081958</v>
+        <v>31.39750788081925</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20">
         <v>29.32728156858283</v>
@@ -2413,7 +2413,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B21">
         <v>24.53475098731074</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B22">
         <v>20.6836399016506</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B23">
         <v>17.15586565945858</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B24">
         <v>16.0591588837813</v>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>14.73224750748778</v>
@@ -2453,15 +2453,15 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B26">
-        <v>13.43059426558227</v>
+        <v>13.43059426558223</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B27">
         <v>12.48695053312343</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B28">
         <v>11.74781658715669</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B29">
         <v>11.25341924613849</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B30">
-        <v>10.29544073589627</v>
+        <v>10.29544073589626</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2501,18 +2501,18 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B32">
-        <v>8.184992379074702</v>
+        <v>8.184992379074686</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33">
-        <v>6.936780389651926</v>
+        <v>6.936780389651807</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2525,15 +2525,15 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B35">
-        <v>6.179403118007395</v>
+        <v>6.179403118007353</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B36">
         <v>4.122012534788953</v>
@@ -2541,18 +2541,18 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B37">
-        <v>3.605153515701735</v>
+        <v>3.605153515701726</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B38">
-        <v>3.555278190690234</v>
+        <v>3.555278190690232</v>
       </c>
     </row>
   </sheetData>
@@ -2578,7 +2578,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>328.6190207717895</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3">
         <v>326.0494693294132</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>42.75428067438558</v>
@@ -2611,7 +2611,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <v>41.87324484419293</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>25.75729442576642</v>
@@ -2644,7 +2644,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8">
         <v>20.42611737638902</v>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B9">
         <v>18.46828252636565</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10">
         <v>12.1962710506586</v>
@@ -2677,7 +2677,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B11">
         <v>9.778753757203608</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>8.110706602095872</v>
@@ -2699,7 +2699,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13">
         <v>7.923688843187629</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <v>7.534019274019623</v>
@@ -2721,10 +2721,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B15">
-        <v>6.250986981492523</v>
+        <v>6.250986981492519</v>
       </c>
       <c r="C15">
         <v>18</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16">
         <v>5.962787458006427</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B17">
         <v>4.426767255194977</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B18">
         <v>2.02520703580745</v>
@@ -2765,10 +2765,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B19">
-        <v>1.979926948591125</v>
+        <v>1.979926948591124</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B20">
         <v>41.87290280834648</v>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B21">
         <v>41.38834843436405</v>
@@ -2798,7 +2798,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B22">
         <v>36.28813888109696</v>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24">
         <v>24.88224502734892</v>
@@ -2831,7 +2831,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B25">
         <v>20.38911572387227</v>
@@ -2842,7 +2842,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B26">
         <v>16.76324080280147</v>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B27">
-        <v>12.18919840526254</v>
+        <v>12.18919840526252</v>
       </c>
       <c r="C27">
         <v>17</v>
@@ -2864,7 +2864,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B28">
         <v>8.941543249683734</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B29">
         <v>8.096953119065038</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B30">
-        <v>7.80286786728263</v>
+        <v>7.802867867282623</v>
       </c>
       <c r="C30">
         <v>17</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B31">
-        <v>6.445186308519587</v>
+        <v>6.445186308519583</v>
       </c>
       <c r="C31">
         <v>17</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32">
         <v>5.94224932585889</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B33">
         <v>5.80782290908279</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B34">
-        <v>4.351265437384765</v>
+        <v>4.351265437384768</v>
       </c>
       <c r="C34">
         <v>17</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B35">
-        <v>1.956215191063303</v>
+        <v>1.956215191063304</v>
       </c>
       <c r="C35">
         <v>17</v>
@@ -2952,7 +2952,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B36">
         <v>1.433111657979802</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B37">
         <v>31.92581828342628</v>
@@ -2974,7 +2974,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B38">
         <v>29.10105604092798</v>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39">
         <v>24.7124415882073</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B41">
-        <v>17.37516368766268</v>
+        <v>17.37516368766272</v>
       </c>
       <c r="C41">
         <v>16</v>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B42">
         <v>12.57042430662915</v>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B43">
         <v>9.930809114650833</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B44">
-        <v>8.916704995121531</v>
+        <v>8.916704995121522</v>
       </c>
       <c r="C44">
         <v>16</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B45">
         <v>8.037106928365864</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B46">
         <v>7.76003933921245</v>
@@ -3073,7 +3073,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B47">
         <v>6.063529971232985</v>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B48">
-        <v>5.934884541195335</v>
+        <v>5.934884541195331</v>
       </c>
       <c r="C48">
         <v>16</v>
@@ -3095,7 +3095,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B49">
         <v>5.606672849834768</v>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B50">
         <v>4.192989756761937</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B51">
         <v>1.95370051405314</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B52">
         <v>1.432796266342846</v>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B53">
         <v>31.84122748155631</v>
@@ -3153,7 +3153,7 @@
         <v>51</v>
       </c>
       <c r="B54">
-        <v>24.21651697444816</v>
+        <v>24.21651697444809</v>
       </c>
       <c r="C54">
         <v>15</v>
@@ -3161,7 +3161,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55">
         <v>24.19050525811368</v>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B56">
         <v>12.46761279135353</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B57">
         <v>9.445798538099208</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B58">
         <v>8.789333686335024</v>
@@ -3205,7 +3205,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B59">
         <v>7.973619177366252</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B60">
-        <v>7.697158278886958</v>
+        <v>7.697158278886951</v>
       </c>
       <c r="C60">
         <v>15</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B61">
         <v>6.564858461468513</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B62">
         <v>5.928433355231266</v>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B63">
         <v>5.392694578619995</v>
@@ -3260,7 +3260,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B64">
         <v>4.186151772503821</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B65">
-        <v>2.471635140572852</v>
+        <v>2.471635140572853</v>
       </c>
       <c r="C65">
         <v>15</v>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B66">
-        <v>1.953644650973072</v>
+        <v>1.953644650973071</v>
       </c>
       <c r="C66">
         <v>15</v>
@@ -3293,10 +3293,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B67">
-        <v>1.40530325996088</v>
+        <v>1.405303259960879</v>
       </c>
       <c r="C67">
         <v>15</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B68">
         <v>22.54677861593612</v>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B69">
-        <v>10.15960246376948</v>
+        <v>10.15960246376949</v>
       </c>
       <c r="C69">
         <v>14</v>
@@ -3326,7 +3326,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B70">
         <v>9.052538571684716</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B71">
         <v>8.737655559807953</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B72">
         <v>7.773135187406902</v>
@@ -3359,10 +3359,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B73">
-        <v>7.697114662154104</v>
+        <v>7.697114662154097</v>
       </c>
       <c r="C73">
         <v>14</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B74">
         <v>7.582889283365247</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B75">
         <v>6.431520964206865</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B76">
-        <v>5.545253422091948</v>
+        <v>5.545253422091944</v>
       </c>
       <c r="C76">
         <v>14</v>
@@ -3403,10 +3403,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B77">
-        <v>5.374637695971954</v>
+        <v>5.374637695971951</v>
       </c>
       <c r="C77">
         <v>14</v>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B78">
         <v>3.234197776257935</v>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B79">
-        <v>2.334493933447929</v>
+        <v>2.334493933447928</v>
       </c>
       <c r="C79">
         <v>14</v>
@@ -3436,7 +3436,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B80">
         <v>1.949651365211263</v>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B81">
         <v>1.400793796367297</v>
@@ -3458,7 +3458,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B82">
         <v>9.036720426049223</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B83">
         <v>8.619731447308707</v>
@@ -3480,7 +3480,7 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B84">
         <v>7.75601214531338</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B85">
         <v>7.597470939743933</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B86">
         <v>7.591424209270143</v>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B87">
         <v>7.137077464490902</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B88">
         <v>5.536130934445319</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B89">
-        <v>5.369596816373703</v>
+        <v>5.369596816373701</v>
       </c>
       <c r="C89">
         <v>13</v>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B90">
         <v>5.297119430349436</v>
@@ -3557,7 +3557,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B91">
         <v>3.206427328735217</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B92">
-        <v>1.946139302455396</v>
+        <v>1.946139302455395</v>
       </c>
       <c r="C92">
         <v>13</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B93">
         <v>1.604938015926638</v>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B94">
-        <v>1.373557923280666</v>
+        <v>1.373557923280665</v>
       </c>
       <c r="C94">
         <v>13</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B2">
         <v>9.036720426049223</v>
@@ -3627,7 +3627,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3">
         <v>8.619731447308707</v>
@@ -3635,7 +3635,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>7.75601214531338</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>7.597470939743933</v>
@@ -3651,7 +3651,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6">
         <v>7.591424209270143</v>
@@ -3659,7 +3659,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B7">
         <v>7.137077464490902</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>5.536130934445319</v>
@@ -3675,15 +3675,15 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9">
-        <v>5.369596816373703</v>
+        <v>5.369596816373701</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10">
         <v>5.297119430349436</v>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>3.206427328735217</v>
@@ -3699,15 +3699,15 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B12">
-        <v>1.946139302455396</v>
+        <v>1.946139302455395</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B13">
         <v>1.604938015926638</v>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B14">
-        <v>1.373557923280666</v>
+        <v>1.373557923280665</v>
       </c>
     </row>
   </sheetData>
@@ -3738,67 +3738,67 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/feature_selection/sinchon/feature_selection_summary.xlsx
+++ b/연구코드/results/feature_selection/sinchon/feature_selection_summary.xlsx
@@ -47,7 +47,7 @@
     <t>VIF pruning (VIF&gt;10)</t>
   </si>
   <si>
-    <t>wavelet_cD2_energy, range, peak_mean_height, p5, wavelet_energy_ratio_D1, fft_mag_std, AUC_normalized, wavelet_cA_energy, spectral_rolloff, mean_abs_deviation, p95, p75, RMSE, valley_count, band1_energy_ratio, band1_energy, band4_energy_ratio, wavelet_cD1_energy, p90, wavelet_cA_std, median, slope_abs_mean, wavelet_cD1_std, band4_energy, fft_mag_mean, peak_max_height, p10, p25</t>
+    <t>peak_mean_height, band4_energy_ratio, median, fft_mag_std, p75, peak_max_height, p10, wavelet_cA_std, fft_mag_mean, mean_abs_deviation, band1_energy_ratio, p95, AUC_normalized, wavelet_cD1_energy, valley_count, p25, range, p5, band4_energy, wavelet_cD2_energy, slope_abs_mean, wavelet_cD1_std, wavelet_energy_ratio_D1, spectral_rolloff, RMSE, wavelet_cA_energy, band1_energy, p90</t>
   </si>
   <si>
     <t>AUC, IQR, fft_mag_max, max, peak_count, peak_max_width, peak_mean_width, signal_energy, skewness, slope_mean, slope_min, spectral_centroid, spectral_energy, spectral_spread, wavelet_cD2_std, wavelet_cD3_energy, zero_crossing_rate</t>
@@ -86,12 +86,12 @@
     <t>vote_ge1</t>
   </si>
   <si>
+    <t>RF_Perm_only</t>
+  </si>
+  <si>
     <t>union_all</t>
   </si>
   <si>
-    <t>RF_Perm_only</t>
-  </si>
-  <si>
     <t>AUC, CV, band2_energy_ratio, max, p90_p10_ratio, peak_mean_width, slope_mean, zero_crossing_rate</t>
   </si>
   <si>
@@ -131,10 +131,13 @@
     <t>p_value</t>
   </si>
   <si>
+    <t>max</t>
+  </si>
+  <si>
     <t>zero_crossing_rate</t>
   </si>
   <si>
-    <t>max</t>
+    <t>CV</t>
   </si>
   <si>
     <t>fft_mag_max</t>
@@ -146,94 +149,91 @@
     <t>slope_mean</t>
   </si>
   <si>
+    <t>peak_mean_width</t>
+  </si>
+  <si>
+    <t>p90_p10_ratio</t>
+  </si>
+  <si>
+    <t>band2_energy_ratio</t>
+  </si>
+  <si>
     <t>AUC</t>
   </si>
   <si>
-    <t>p90_p10_ratio</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>peak_mean_width</t>
-  </si>
-  <si>
-    <t>band2_energy_ratio</t>
+    <t>slope_std</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>slope_max</t>
+  </si>
+  <si>
+    <t>signal_energy</t>
+  </si>
+  <si>
+    <t>peak_count</t>
+  </si>
+  <si>
+    <t>band3_energy_ratio</t>
+  </si>
+  <si>
+    <t>signal_length</t>
+  </si>
+  <si>
+    <t>kurtosis</t>
+  </si>
+  <si>
+    <t>band2_energy</t>
+  </si>
+  <si>
+    <t>peak_max_width</t>
+  </si>
+  <si>
+    <t>peak_main_pos</t>
+  </si>
+  <si>
+    <t>wavelet_cD2_std</t>
+  </si>
+  <si>
+    <t>slope_min</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>spectral_energy</t>
+  </si>
+  <si>
+    <t>wavelet_cD3_energy</t>
+  </si>
+  <si>
+    <t>first_high_pos</t>
+  </si>
+  <si>
+    <t>IQR</t>
+  </si>
+  <si>
+    <t>wavelet_cD3_std</t>
+  </si>
+  <si>
+    <t>spectral_spread</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>skewness</t>
   </si>
   <si>
     <t>dominant_freq</t>
   </si>
   <si>
-    <t>band3_energy_ratio</t>
-  </si>
-  <si>
-    <t>peak_max_width</t>
-  </si>
-  <si>
-    <t>peak_count</t>
-  </si>
-  <si>
-    <t>IQR</t>
-  </si>
-  <si>
-    <t>spectral_spread</t>
-  </si>
-  <si>
-    <t>wavelet_cD3_energy</t>
-  </si>
-  <si>
-    <t>slope_std</t>
-  </si>
-  <si>
-    <t>signal_energy</t>
-  </si>
-  <si>
-    <t>kurtosis</t>
-  </si>
-  <si>
-    <t>first_high_pos</t>
-  </si>
-  <si>
-    <t>wavelet_cD3_std</t>
-  </si>
-  <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>band2_energy</t>
-  </si>
-  <si>
-    <t>slope_max</t>
-  </si>
-  <si>
-    <t>peak_main_pos</t>
-  </si>
-  <si>
-    <t>slope_min</t>
-  </si>
-  <si>
-    <t>skewness</t>
-  </si>
-  <si>
-    <t>wavelet_cD2_std</t>
-  </si>
-  <si>
-    <t>spectral_energy</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>signal_length</t>
-  </si>
-  <si>
-    <t>std</t>
+    <t>peak_std_height</t>
   </si>
   <si>
     <t>peak_last_pos</t>
-  </si>
-  <si>
-    <t>peak_std_height</t>
   </si>
   <si>
     <t>peak_first_pos</t>
@@ -701,7 +701,7 @@
         <v>17</v>
       </c>
       <c r="C2">
-        <v>0.098763750553166</v>
+        <v>0.09876375055316607</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -729,7 +729,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>0.07513415392997244</v>
+        <v>0.07513415392997251</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -743,7 +743,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>0.05922520891076235</v>
+        <v>0.05922520891076246</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
@@ -757,7 +757,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0.05771111288514301</v>
+        <v>0.05771111288514297</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -771,7 +771,7 @@
         <v>33</v>
       </c>
       <c r="C7">
-        <v>-0.1477814951767644</v>
+        <v>-0.1477814951767659</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
@@ -785,7 +785,7 @@
         <v>33</v>
       </c>
       <c r="C8">
-        <v>-0.1477814951767654</v>
+        <v>-0.14778149517677</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
@@ -799,7 +799,7 @@
         <v>33</v>
       </c>
       <c r="C9">
-        <v>-0.1477814951767658</v>
+        <v>-0.1477814951767708</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
@@ -858,13 +858,13 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.0654025856735676</v>
+        <v>0.01060986752624382</v>
       </c>
       <c r="G2">
-        <v>0.1785938877945625</v>
+        <v>0.1997601737185831</v>
       </c>
       <c r="H2">
-        <v>1.432264850401951E-10</v>
+        <v>6.612496588809641E-13</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -884,13 +884,13 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.01060986752624382</v>
+        <v>0.0654025856735676</v>
       </c>
       <c r="G3">
-        <v>0.1997601737185831</v>
+        <v>0.1785938877945625</v>
       </c>
       <c r="H3">
-        <v>6.612496588809641E-13</v>
+        <v>1.432264850401951E-10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -901,22 +901,22 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>0.0170287002512044</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0.01414262849277602</v>
+        <v>-0.131354028217828</v>
       </c>
       <c r="H4">
-        <v>0.6144517034028094</v>
+        <v>2.618507265846386E-06</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -936,13 +936,13 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.001738440350150139</v>
+        <v>0.0170287002512044</v>
       </c>
       <c r="G5">
-        <v>0.06119722045541939</v>
+        <v>0.01414262849277602</v>
       </c>
       <c r="H5">
-        <v>0.02913568790884516</v>
+        <v>0.6144517034028094</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -953,22 +953,22 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.001738440350150139</v>
       </c>
       <c r="G6">
-        <v>0.06899528972260857</v>
+        <v>0.06119722045541939</v>
       </c>
       <c r="H6">
-        <v>0.01388328883776795</v>
+        <v>0.02913568790884516</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -988,13 +988,13 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.02685575363017101</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0.2158179640102999</v>
+        <v>0.06899528972260857</v>
       </c>
       <c r="H7">
-        <v>7.343747734458469E-15</v>
+        <v>0.01388328883776795</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1014,13 +1014,13 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.02467660868363675</v>
+        <v>0.01760399500620879</v>
       </c>
       <c r="G8">
-        <v>-0.1223260580122692</v>
+        <v>0.01376479737486372</v>
       </c>
       <c r="H8">
-        <v>1.224391247864785E-05</v>
+        <v>0.6239425888046031</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1040,13 +1040,13 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.02467660868363675</v>
       </c>
       <c r="G9">
-        <v>-0.131354028217828</v>
+        <v>-0.1223260580122692</v>
       </c>
       <c r="H9">
-        <v>2.618507265846387E-06</v>
+        <v>1.224391247864785E-05</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0.01760399500620879</v>
+        <v>0.05680607666697224</v>
       </c>
       <c r="G10">
-        <v>0.01376479737486372</v>
+        <v>0.009097645213949538</v>
       </c>
       <c r="H10">
-        <v>0.6239425888046031</v>
+        <v>0.7459164427607015</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1092,13 +1092,13 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0.05680607666697224</v>
+        <v>0.02685575363017101</v>
       </c>
       <c r="G11">
-        <v>0.009097645213949538</v>
+        <v>0.2158179640102999</v>
       </c>
       <c r="H11">
-        <v>0.7459164427607015</v>
+        <v>7.343747734458469E-15</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1118,13 +1118,13 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>0.07376464842085761</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>-0.05862626251613298</v>
+        <v>0.2045972503771621</v>
       </c>
       <c r="H12">
-        <v>0.03663297245911071</v>
+        <v>1.771735228659869E-13</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1144,13 +1144,13 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>0.009241468356806948</v>
+        <v>0.03796568588434379</v>
       </c>
       <c r="G13">
-        <v>-0.001140861960857506</v>
+        <v>0.03275000019090109</v>
       </c>
       <c r="H13">
-        <v>0.9675885050856522</v>
+        <v>0.2433164866149352</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1170,13 +1170,13 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>0.01931159189417242</v>
+        <v>0.003065626782587927</v>
       </c>
       <c r="G14">
-        <v>0.1003944159289539</v>
+        <v>0.2124966331294762</v>
       </c>
       <c r="H14">
-        <v>0.0003374551254947321</v>
+        <v>1.919939657764731E-14</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>0.01697616447823336</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>0.08922313682577719</v>
+        <v>0.2216348340319491</v>
       </c>
       <c r="H15">
-        <v>0.001451926713498682</v>
+        <v>1.313079481857501E-15</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1222,13 +1222,13 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>0.0001064739115430591</v>
+        <v>0.01697616447823336</v>
       </c>
       <c r="G16">
-        <v>-0.02209183542907095</v>
+        <v>0.08922313682577719</v>
       </c>
       <c r="H16">
-        <v>0.431329258732049</v>
+        <v>0.001451926713498682</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1248,13 +1248,13 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>0.0100516165813227</v>
+        <v>0.009241468356806948</v>
       </c>
       <c r="G17">
-        <v>0.000204487370416031</v>
+        <v>-0.001140861960857506</v>
       </c>
       <c r="H17">
-        <v>0.9941890388816222</v>
+        <v>0.9675885050856522</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1274,13 +1274,13 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>0.01244173464559628</v>
+        <v>0.08346266882108866</v>
       </c>
       <c r="G18">
-        <v>0.133370110268565</v>
+        <v>0.1874827253801424</v>
       </c>
       <c r="H18">
-        <v>1.829119265022864E-06</v>
+        <v>1.614546679236788E-11</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1300,13 +1300,13 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>0.02317873999776143</v>
       </c>
       <c r="G19">
-        <v>0.2045972503771621</v>
+        <v>0.1840964913884834</v>
       </c>
       <c r="H19">
-        <v>1.771735228659869E-13</v>
+        <v>3.756308236071874E-11</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>0.005520957338708055</v>
       </c>
       <c r="G20">
-        <v>0.2216348340319491</v>
+        <v>0.03846285222041766</v>
       </c>
       <c r="H20">
-        <v>1.313079481857501E-15</v>
+        <v>0.1705619525091443</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1352,13 +1352,13 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>0.02317873999776143</v>
+        <v>0.01931159189417242</v>
       </c>
       <c r="G21">
-        <v>0.1840964913884834</v>
+        <v>0.1003944159289539</v>
       </c>
       <c r="H21">
-        <v>3.756308236071874E-11</v>
+        <v>0.0003374551254947321</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1378,13 +1378,13 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>0.02183813124742073</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>0.02520720991881296</v>
+        <v>0.07162353270483773</v>
       </c>
       <c r="H22">
-        <v>0.3692266617451235</v>
+        <v>0.01064243788129301</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1404,13 +1404,13 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>0.05248366657931935</v>
       </c>
       <c r="G23">
-        <v>0.116408059406549</v>
+        <v>0.1733840996662887</v>
       </c>
       <c r="H23">
-        <v>3.180513501099746E-05</v>
+        <v>4.894997707133988E-10</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1430,13 +1430,13 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>0.03670529154184354</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>0.2238189057127703</v>
+        <v>-0.1840675505765382</v>
       </c>
       <c r="H24">
-        <v>6.793151437168481E-16</v>
+        <v>3.783255740618084E-11</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>0.005520957338708055</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>0.03846285222041766</v>
+        <v>0.2311231494201107</v>
       </c>
       <c r="H25">
-        <v>0.1705619525091443</v>
+        <v>7.126123145518417E-17</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1482,13 +1482,13 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>0.003065626782587927</v>
+        <v>0.02665402921515936</v>
       </c>
       <c r="G26">
-        <v>0.2124966331294762</v>
+        <v>0.05227088441037193</v>
       </c>
       <c r="H26">
-        <v>1.919939657764731E-14</v>
+        <v>0.06246875221612761</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1508,13 +1508,13 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>0.01244173464559628</v>
       </c>
       <c r="G27">
-        <v>0.07162353270483773</v>
+        <v>0.133370110268565</v>
       </c>
       <c r="H27">
-        <v>0.01064243788129301</v>
+        <v>1.829119265022864E-06</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1534,13 +1534,13 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>0.02183813124742073</v>
       </c>
       <c r="G28">
-        <v>-0.1840675505765382</v>
+        <v>0.02520720991881296</v>
       </c>
       <c r="H28">
-        <v>3.783255740618084E-11</v>
+        <v>0.3692266617451234</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1560,13 +1560,13 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>0.00416031262364136</v>
+        <v>0.0001064739115430591</v>
       </c>
       <c r="G29">
-        <v>-0.06016177884717459</v>
+        <v>-0.02209183542907095</v>
       </c>
       <c r="H29">
-        <v>0.03197962040409953</v>
+        <v>0.431329258732049</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>0.05248366657931935</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>0.1733840996662887</v>
+        <v>0.116408059406549</v>
       </c>
       <c r="H30">
-        <v>4.894997707133989E-10</v>
+        <v>3.180513501099747E-05</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1612,13 +1612,13 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>0.02665402921515936</v>
+        <v>0.0100516165813227</v>
       </c>
       <c r="G31">
-        <v>0.05227088441037193</v>
+        <v>0.000204487370416031</v>
       </c>
       <c r="H31">
-        <v>0.06246875221612761</v>
+        <v>0.9941890388816222</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1638,13 +1638,13 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>0.03670529154184354</v>
       </c>
       <c r="G32">
-        <v>0.2311231494201107</v>
+        <v>0.2238189057127703</v>
       </c>
       <c r="H32">
-        <v>7.126123145518417E-17</v>
+        <v>6.793151437168481E-16</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1664,13 +1664,13 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>0.08346266882108866</v>
+        <v>0.00416031262364136</v>
       </c>
       <c r="G33">
-        <v>0.1874827253801424</v>
+        <v>-0.06016177884717459</v>
       </c>
       <c r="H33">
-        <v>1.614546679236788E-11</v>
+        <v>0.03197962040409952</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1690,13 +1690,13 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>0.03796568588434379</v>
+        <v>0.07376464842085761</v>
       </c>
       <c r="G34">
-        <v>0.03275000019090109</v>
+        <v>-0.05862626251613298</v>
       </c>
       <c r="H34">
-        <v>0.2433164866149352</v>
+        <v>0.03663297245911071</v>
       </c>
     </row>
   </sheetData>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B2">
         <v>0.08346266882108866</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B3">
         <v>0.07376464842085761</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>0.0654025856735676</v>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>0.05680607666697224</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B6">
         <v>0.05248366657931935</v>
@@ -1790,12 +1790,12 @@
         <v>0.1733840996662887</v>
       </c>
       <c r="D6">
-        <v>4.894997707133989E-10</v>
+        <v>4.894997707133988E-10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B7">
         <v>0.03796568588434379</v>
@@ -1809,7 +1809,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B8">
         <v>0.03670529154184354</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <v>0.02685575363017101</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B10">
         <v>0.02665402921515936</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>0.02467660868363675</v>
@@ -1865,7 +1865,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B12">
         <v>0.02317873999776143</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B13">
         <v>0.02183813124742073</v>
@@ -1888,12 +1888,12 @@
         <v>0.02520720991881296</v>
       </c>
       <c r="D13">
-        <v>0.3692266617451235</v>
+        <v>0.3692266617451234</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>0.01931159189417242</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>0.01760399500620879</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16">
         <v>0.0170287002512044</v>
@@ -1935,7 +1935,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>0.01697616447823336</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B18">
         <v>0.01244173464559628</v>
@@ -1963,7 +1963,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19">
         <v>0.01060986752624382</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B20">
         <v>0.0100516165813227</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B21">
         <v>0.009241468356806948</v>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B22">
         <v>0.005520957338708055</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B23">
         <v>0.00416031262364136</v>
@@ -2028,12 +2028,12 @@
         <v>-0.06016177884717459</v>
       </c>
       <c r="D23">
-        <v>0.03197962040409953</v>
+        <v>0.03197962040409952</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B24">
         <v>0.003065626782587927</v>
@@ -2047,7 +2047,7 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25">
         <v>0.001738440350150139</v>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B26">
         <v>0.0001064739115430591</v>
@@ -2075,21 +2075,21 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.02782971538947907</v>
+        <v>0.2311231494201107</v>
       </c>
       <c r="D27">
-        <v>0.3215023059479291</v>
+        <v>7.126123145518417E-17</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2098,12 +2098,12 @@
         <v>-0.131354028217828</v>
       </c>
       <c r="D28">
-        <v>2.618507265846387E-06</v>
+        <v>2.618507265846386E-06</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2131,86 +2131,86 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>-0.001178186297915739</v>
+        <v>0.2045972503771621</v>
       </c>
       <c r="D31">
-        <v>0.9665287451927558</v>
+        <v>1.771735228659869E-13</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>0.2311231494201107</v>
+        <v>0.06899528972260857</v>
       </c>
       <c r="D32">
-        <v>7.126123145518417E-17</v>
+        <v>0.01388328883776795</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0.07162353270483773</v>
+        <v>0.02782971538947907</v>
       </c>
       <c r="D33">
-        <v>0.01064243788129301</v>
+        <v>0.3215023059479291</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0.2045972503771621</v>
+        <v>0.07162353270483773</v>
       </c>
       <c r="D34">
-        <v>1.771735228659869E-13</v>
+        <v>0.01064243788129301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>-0.1840675505765382</v>
+        <v>-0.001178186297915739</v>
       </c>
       <c r="D35">
-        <v>3.783255740618084E-11</v>
+        <v>0.9665287451927558</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0.116408059406549</v>
+        <v>-0.1840675505765382</v>
       </c>
       <c r="D36">
-        <v>3.180513501099746E-05</v>
+        <v>3.783255740618084E-11</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2229,16 +2229,16 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0.06899528972260857</v>
+        <v>0.116408059406549</v>
       </c>
       <c r="D38">
-        <v>0.01388328883776795</v>
+        <v>3.180513501099747E-05</v>
       </c>
     </row>
   </sheetData>
@@ -2261,7 +2261,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2">
         <v>1289.284989699355</v>
@@ -2269,7 +2269,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <v>766.229327687265</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B4">
         <v>363.4626769355639</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B5">
         <v>316.4109499953126</v>
@@ -2293,23 +2293,23 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6">
-        <v>159.0133372106722</v>
+        <v>159.0133372106835</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7">
-        <v>148.7113016225222</v>
+        <v>148.7113016225247</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>147.5171717141093</v>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>121.4257923588872</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>96.13214918834973</v>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>82.42884405187472</v>
@@ -2349,15 +2349,15 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B13">
-        <v>73.95926549583329</v>
+        <v>73.9592654958339</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <v>71.79632406955261</v>
@@ -2365,15 +2365,15 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B15">
-        <v>58.59776609909582</v>
+        <v>58.59776609909621</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B16">
         <v>58.31107383422511</v>
@@ -2381,31 +2381,31 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B17">
-        <v>52.91039906801186</v>
+        <v>52.91039906801216</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B18">
-        <v>33.03756809422122</v>
+        <v>33.03756809422134</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B19">
-        <v>31.39750788081925</v>
+        <v>31.39750788081958</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B20">
         <v>29.32728156858283</v>
@@ -2413,7 +2413,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B21">
         <v>24.53475098731074</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B22">
         <v>20.6836399016506</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B23">
         <v>17.15586565945858</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>16.0591588837813</v>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25">
         <v>14.73224750748778</v>
@@ -2453,15 +2453,15 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B26">
-        <v>13.43059426558223</v>
+        <v>13.43059426558227</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B27">
         <v>12.48695053312343</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B28">
         <v>11.74781658715669</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B29">
         <v>11.25341924613849</v>
@@ -2485,15 +2485,15 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B30">
-        <v>10.29544073589626</v>
+        <v>10.29544073589627</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B31">
         <v>8.249551284409103</v>
@@ -2501,18 +2501,18 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32">
-        <v>8.184992379074686</v>
+        <v>8.184992379074702</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B33">
-        <v>6.936780389651807</v>
+        <v>6.936780389651926</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2525,15 +2525,15 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B35">
-        <v>6.179403118007353</v>
+        <v>6.179403118007395</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B36">
         <v>4.122012534788953</v>
@@ -2541,18 +2541,18 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B37">
-        <v>3.605153515701726</v>
+        <v>3.605153515701735</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B38">
-        <v>3.555278190690232</v>
+        <v>3.555278190690234</v>
       </c>
     </row>
   </sheetData>
@@ -2578,7 +2578,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2">
         <v>328.6190207717895</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <v>326.0494693294132</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>42.75428067438558</v>
@@ -2611,7 +2611,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>41.87324484419293</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>25.75729442576642</v>
@@ -2633,7 +2633,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B7">
         <v>25.66458474694967</v>
@@ -2644,7 +2644,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B8">
         <v>20.42611737638902</v>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B9">
         <v>18.46828252636565</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B10">
         <v>12.1962710506586</v>
@@ -2677,7 +2677,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B11">
         <v>9.778753757203608</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B12">
         <v>8.110706602095872</v>
@@ -2699,7 +2699,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B13">
         <v>7.923688843187629</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B14">
         <v>7.534019274019623</v>
@@ -2721,10 +2721,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15">
-        <v>6.250986981492519</v>
+        <v>6.250986981492523</v>
       </c>
       <c r="C15">
         <v>18</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16">
         <v>5.962787458006427</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17">
         <v>4.426767255194977</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B18">
         <v>2.02520703580745</v>
@@ -2765,10 +2765,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B19">
-        <v>1.979926948591124</v>
+        <v>1.979926948591125</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B20">
         <v>41.87290280834648</v>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21">
         <v>41.38834843436405</v>
@@ -2798,7 +2798,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B22">
         <v>36.28813888109696</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B23">
         <v>25.10452393526627</v>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24">
         <v>24.88224502734892</v>
@@ -2831,7 +2831,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B25">
         <v>20.38911572387227</v>
@@ -2842,7 +2842,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B26">
         <v>16.76324080280147</v>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B27">
-        <v>12.18919840526252</v>
+        <v>12.18919840526254</v>
       </c>
       <c r="C27">
         <v>17</v>
@@ -2864,7 +2864,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B28">
         <v>8.941543249683734</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B29">
         <v>8.096953119065038</v>
@@ -2886,10 +2886,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B30">
-        <v>7.802867867282623</v>
+        <v>7.80286786728263</v>
       </c>
       <c r="C30">
         <v>17</v>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B31">
-        <v>6.445186308519583</v>
+        <v>6.445186308519587</v>
       </c>
       <c r="C31">
         <v>17</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32">
         <v>5.94224932585889</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B33">
         <v>5.80782290908279</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34">
-        <v>4.351265437384768</v>
+        <v>4.351265437384765</v>
       </c>
       <c r="C34">
         <v>17</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B35">
-        <v>1.956215191063304</v>
+        <v>1.956215191063303</v>
       </c>
       <c r="C35">
         <v>17</v>
@@ -2952,7 +2952,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B36">
         <v>1.433111657979802</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B37">
         <v>31.92581828342628</v>
@@ -2974,7 +2974,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38">
         <v>29.10105604092798</v>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39">
         <v>24.7124415882073</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B40">
         <v>24.41952041322764</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B41">
-        <v>17.37516368766272</v>
+        <v>17.37516368766268</v>
       </c>
       <c r="C41">
         <v>16</v>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B42">
         <v>12.57042430662915</v>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B43">
         <v>9.930809114650833</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B44">
-        <v>8.916704995121522</v>
+        <v>8.916704995121531</v>
       </c>
       <c r="C44">
         <v>16</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B45">
         <v>8.037106928365864</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B46">
         <v>7.76003933921245</v>
@@ -3073,7 +3073,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B47">
         <v>6.063529971232985</v>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B48">
-        <v>5.934884541195331</v>
+        <v>5.934884541195335</v>
       </c>
       <c r="C48">
         <v>16</v>
@@ -3095,7 +3095,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B49">
         <v>5.606672849834768</v>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B50">
         <v>4.192989756761937</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B51">
         <v>1.95370051405314</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B52">
         <v>1.432796266342846</v>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B53">
         <v>31.84122748155631</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B54">
-        <v>24.21651697444809</v>
+        <v>24.21651697444816</v>
       </c>
       <c r="C54">
         <v>15</v>
@@ -3161,7 +3161,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B55">
         <v>24.19050525811368</v>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B56">
         <v>12.46761279135353</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B57">
         <v>9.445798538099208</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B58">
         <v>8.789333686335024</v>
@@ -3205,7 +3205,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B59">
         <v>7.973619177366252</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B60">
-        <v>7.697158278886951</v>
+        <v>7.697158278886958</v>
       </c>
       <c r="C60">
         <v>15</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B61">
         <v>6.564858461468513</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B62">
         <v>5.928433355231266</v>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B63">
         <v>5.392694578619995</v>
@@ -3260,7 +3260,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B64">
         <v>4.186151772503821</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B65">
-        <v>2.471635140572853</v>
+        <v>2.471635140572852</v>
       </c>
       <c r="C65">
         <v>15</v>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B66">
-        <v>1.953644650973071</v>
+        <v>1.953644650973072</v>
       </c>
       <c r="C66">
         <v>15</v>
@@ -3293,10 +3293,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B67">
-        <v>1.405303259960879</v>
+        <v>1.40530325996088</v>
       </c>
       <c r="C67">
         <v>15</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B68">
         <v>22.54677861593612</v>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B69">
-        <v>10.15960246376949</v>
+        <v>10.15960246376948</v>
       </c>
       <c r="C69">
         <v>14</v>
@@ -3326,7 +3326,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B70">
         <v>9.052538571684716</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B71">
         <v>8.737655559807953</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B72">
         <v>7.773135187406902</v>
@@ -3359,10 +3359,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B73">
-        <v>7.697114662154097</v>
+        <v>7.697114662154104</v>
       </c>
       <c r="C73">
         <v>14</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B74">
         <v>7.582889283365247</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B75">
         <v>6.431520964206865</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B76">
-        <v>5.545253422091944</v>
+        <v>5.545253422091948</v>
       </c>
       <c r="C76">
         <v>14</v>
@@ -3403,10 +3403,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B77">
-        <v>5.374637695971951</v>
+        <v>5.374637695971954</v>
       </c>
       <c r="C77">
         <v>14</v>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B78">
         <v>3.234197776257935</v>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B79">
-        <v>2.334493933447928</v>
+        <v>2.334493933447929</v>
       </c>
       <c r="C79">
         <v>14</v>
@@ -3436,7 +3436,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B80">
         <v>1.949651365211263</v>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B81">
         <v>1.400793796367297</v>
@@ -3458,7 +3458,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B82">
         <v>9.036720426049223</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B83">
         <v>8.619731447308707</v>
@@ -3480,7 +3480,7 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B84">
         <v>7.75601214531338</v>
@@ -3491,7 +3491,7 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B85">
         <v>7.597470939743933</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B86">
         <v>7.591424209270143</v>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B87">
         <v>7.137077464490902</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B88">
         <v>5.536130934445319</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B89">
-        <v>5.369596816373701</v>
+        <v>5.369596816373703</v>
       </c>
       <c r="C89">
         <v>13</v>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B90">
         <v>5.297119430349436</v>
@@ -3557,7 +3557,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B91">
         <v>3.206427328735217</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B92">
-        <v>1.946139302455395</v>
+        <v>1.946139302455396</v>
       </c>
       <c r="C92">
         <v>13</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B93">
         <v>1.604938015926638</v>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B94">
-        <v>1.373557923280665</v>
+        <v>1.373557923280666</v>
       </c>
       <c r="C94">
         <v>13</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B2">
         <v>9.036720426049223</v>
@@ -3627,7 +3627,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <v>8.619731447308707</v>
@@ -3635,7 +3635,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>7.75601214531338</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>7.597470939743933</v>
@@ -3651,7 +3651,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B6">
         <v>7.591424209270143</v>
@@ -3659,7 +3659,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B7">
         <v>7.137077464490902</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8">
         <v>5.536130934445319</v>
@@ -3675,15 +3675,15 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9">
-        <v>5.369596816373701</v>
+        <v>5.369596816373703</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B10">
         <v>5.297119430349436</v>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>3.206427328735217</v>
@@ -3699,15 +3699,15 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B12">
-        <v>1.946139302455395</v>
+        <v>1.946139302455396</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B13">
         <v>1.604938015926638</v>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B14">
-        <v>1.373557923280665</v>
+        <v>1.373557923280666</v>
       </c>
     </row>
   </sheetData>
@@ -3738,67 +3738,67 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
